--- a/experiments/results/resnet34/CIFAR-10/baseline/msp/adaptive/max/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/baseline/msp/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -666,6 +666,55 @@
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=4.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>90.63</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>95.97</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>96.06</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
